--- a/data/trans_dic/P12_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,45</t>
+          <t>8,29; 13,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,01</t>
+          <t>7,31; 12,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,14</t>
+          <t>5,0; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,61</t>
+          <t>2,31; 11,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,38; 19,84</t>
+          <t>13,35; 19,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,92</t>
+          <t>14,32; 21,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,82</t>
+          <t>7,78; 13,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 19,88</t>
+          <t>8,05; 19,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,78</t>
+          <t>11,42; 15,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 16,1</t>
+          <t>11,45; 16,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 10,94</t>
+          <t>6,8; 10,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 12,5</t>
+          <t>6,53; 12,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 17,12</t>
+          <t>12,06; 17,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,01</t>
+          <t>11,14; 16,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,83</t>
+          <t>7,16; 12,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 13,18</t>
+          <t>5,83; 12,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,81</t>
+          <t>16,39; 22,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 23,46</t>
+          <t>17,19; 23,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,72</t>
+          <t>9,51; 14,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,82</t>
+          <t>6,71; 14,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 18,55</t>
+          <t>14,63; 18,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,89</t>
+          <t>14,68; 18,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,54</t>
+          <t>8,91; 12,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 12,25</t>
+          <t>7,23; 12,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,34</t>
+          <t>15,25; 21,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,89</t>
+          <t>13,98; 20,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,84</t>
+          <t>7,13; 11,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 14,53</t>
+          <t>9,02; 14,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 25,45</t>
+          <t>19,05; 25,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,46; 28,52</t>
+          <t>21,51; 28,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 15,04</t>
+          <t>10,05; 15,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 19,4</t>
+          <t>13,88; 19,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 22,49</t>
+          <t>17,97; 22,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 23,08</t>
+          <t>18,61; 23,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 12,52</t>
+          <t>9,15; 12,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 15,92</t>
+          <t>12,19; 15,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 21,6</t>
+          <t>14,96; 21,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,65</t>
+          <t>12,53; 18,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 17,75</t>
+          <t>11,8; 17,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,63</t>
+          <t>4,09; 15,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 26,87</t>
+          <t>19,66; 27,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 32,74</t>
+          <t>25,08; 32,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,77</t>
+          <t>12,92; 18,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,1</t>
+          <t>15,38; 21,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 23,14</t>
+          <t>17,9; 22,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,65; 24,39</t>
+          <t>19,8; 24,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 17,08</t>
+          <t>13,1; 17,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 17,34</t>
+          <t>8,75; 17,53</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,48; 25,47</t>
+          <t>17,24; 25,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 24,2</t>
+          <t>16,48; 24,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 16,06</t>
+          <t>9,67; 15,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 21,32</t>
+          <t>15,17; 21,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,58; 31,1</t>
+          <t>22,65; 31,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 32,95</t>
+          <t>24,21; 33,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,93; 25,49</t>
+          <t>17,49; 25,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,64; 26,08</t>
+          <t>20,56; 25,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,18; 27,59</t>
+          <t>21,13; 27,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 27,53</t>
+          <t>21,33; 27,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,49; 19,49</t>
+          <t>14,55; 19,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,58; 22,7</t>
+          <t>18,68; 22,57</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,49; 22,14</t>
+          <t>13,61; 22,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 20,6</t>
+          <t>11,64; 20,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,15</t>
+          <t>10,72; 18,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,79; 18,91</t>
+          <t>12,91; 18,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,16; 32,14</t>
+          <t>23,56; 32,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,27; 33,65</t>
+          <t>23,74; 33,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 25,64</t>
+          <t>17,33; 25,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,05; 77,87</t>
+          <t>19,86; 79,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,97; 26,6</t>
+          <t>19,93; 26,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,46; 26,33</t>
+          <t>19,5; 26,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,16; 20,79</t>
+          <t>15,27; 20,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,54; 67,85</t>
+          <t>17,55; 66,83</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,39; 32,0</t>
+          <t>20,16; 31,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,56; 28,84</t>
+          <t>17,21; 28,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 23,58</t>
+          <t>14,85; 23,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,39; 24,71</t>
+          <t>17,62; 25,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,96; 30,33</t>
+          <t>20,6; 31,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,27; 41,12</t>
+          <t>30,8; 40,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,18; 33,64</t>
+          <t>22,78; 33,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,04</t>
+          <t>26,81; 32,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,89; 29,7</t>
+          <t>21,91; 29,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,37; 34,79</t>
+          <t>27,35; 35,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,87; 28,31</t>
+          <t>21,18; 27,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,84; 28,64</t>
+          <t>23,96; 28,74</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,21</t>
+          <t>15,67; 18,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,05</t>
+          <t>14,58; 17,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,77</t>
+          <t>10,56; 12,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,06</t>
+          <t>9,87; 14,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,79</t>
+          <t>21,05; 23,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,45; 27,51</t>
+          <t>24,55; 27,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,38; 18,03</t>
+          <t>15,43; 18,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,01</t>
+          <t>18,47; 38,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,82</t>
+          <t>18,77; 20,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,97; 22,05</t>
+          <t>20,01; 22,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,12</t>
+          <t>13,41; 15,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,19; 26,29</t>
+          <t>15,23; 26,56</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41130; 66467</t>
+          <t>40958; 67823</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33123; 59083</t>
+          <t>33221; 58904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20194; 42537</t>
+          <t>20957; 42796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11443; 46442</t>
+          <t>9221; 44282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62548; 92740</t>
+          <t>62416; 93047</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61547; 93859</t>
+          <t>61322; 92625</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30132; 54674</t>
+          <t>30777; 53224</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27760; 62256</t>
+          <t>25209; 60624</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>110162; 151721</t>
+          <t>109818; 152429</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102381; 142059</t>
+          <t>101012; 143920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57307; 89204</t>
+          <t>55429; 86237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44671; 89145</t>
+          <t>46566; 92430</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88033; 125939</t>
+          <t>88683; 125135</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78266; 116870</t>
+          <t>76558; 114283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40935; 69839</t>
+          <t>42293; 71493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24317; 55826</t>
+          <t>24714; 54658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>101323; 142659</t>
+          <t>102547; 140507</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104172; 142933</t>
+          <t>104704; 146129</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54145; 82935</t>
+          <t>53619; 83883</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33027; 70686</t>
+          <t>34312; 71698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200064; 252457</t>
+          <t>199081; 255029</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>188985; 244869</t>
+          <t>190260; 243823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102467; 144668</t>
+          <t>102793; 143809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64340; 114552</t>
+          <t>67613; 115046</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96858; 136292</t>
+          <t>97395; 135084</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97534; 135613</t>
+          <t>95319; 137305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49369; 79252</t>
+          <t>47700; 79764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48209; 77954</t>
+          <t>48355; 78470</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130228; 175522</t>
+          <t>131386; 176769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152159; 202196</t>
+          <t>152460; 198541</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65408; 99084</t>
+          <t>66225; 99331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76379; 105225</t>
+          <t>75279; 104117</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>236778; 298784</t>
+          <t>238652; 295707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>258850; 321056</t>
+          <t>258827; 321221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120809; 166293</t>
+          <t>121463; 167348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131633; 171692</t>
+          <t>131475; 170702</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78044; 112146</t>
+          <t>77675; 113431</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74387; 114387</t>
+          <t>76865; 115138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76585; 114477</t>
+          <t>76111; 110559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38531; 138753</t>
+          <t>36322; 139869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>99366; 138542</t>
+          <t>101349; 140559</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>155552; 201114</t>
+          <t>154029; 199415</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82624; 121847</t>
+          <t>83878; 121265</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111593; 150444</t>
+          <t>109624; 150805</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185606; 239485</t>
+          <t>185210; 237358</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>241200; 299458</t>
+          <t>243054; 303857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166143; 221047</t>
+          <t>169513; 221487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>128933; 277494</t>
+          <t>140026; 280522</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67595; 98502</t>
+          <t>66670; 99589</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70237; 103931</t>
+          <t>70770; 104016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46763; 76579</t>
+          <t>46102; 76176</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85062; 119631</t>
+          <t>85112; 118127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91221; 125652</t>
+          <t>91506; 126945</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108715; 147554</t>
+          <t>108430; 148384</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88659; 126094</t>
+          <t>86502; 125268</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113114; 142904</t>
+          <t>112640; 141468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>167457; 218165</t>
+          <t>167060; 215358</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190097; 241486</t>
+          <t>187101; 239402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140799; 189305</t>
+          <t>141381; 189268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>206056; 251725</t>
+          <t>207179; 250307</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39471; 64775</t>
+          <t>39812; 65537</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36378; 63612</t>
+          <t>35944; 62311</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34531; 60690</t>
+          <t>35835; 61030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46974; 69471</t>
+          <t>47439; 67803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79419; 110226</t>
+          <t>80798; 112192</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85676; 118780</t>
+          <t>83780; 118538</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65933; 96846</t>
+          <t>65484; 97384</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>121839; 473304</t>
+          <t>120722; 482608</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126921; 169019</t>
+          <t>126635; 170184</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128766; 174249</t>
+          <t>129028; 172771</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107949; 148012</t>
+          <t>108743; 147302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>171084; 661616</t>
+          <t>171147; 651727</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42795; 67152</t>
+          <t>42306; 66002</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43702; 71784</t>
+          <t>42834; 71493</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37797; 60606</t>
+          <t>38173; 60553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49185; 69868</t>
+          <t>49830; 71258</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69985; 101275</t>
+          <t>68775; 103612</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>121633; 159931</t>
+          <t>119821; 159019</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92481; 134198</t>
+          <t>90880; 132620</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>113079; 140533</t>
+          <t>114062; 138983</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119052; 161531</t>
+          <t>119146; 158838</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174583; 221923</t>
+          <t>174486; 224054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136899; 185712</t>
+          <t>138943; 182558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>168839; 202834</t>
+          <t>169710; 203518</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>511610; 596679</t>
+          <t>513326; 598104</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>495880; 583831</t>
+          <t>499111; 596268</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>354814; 433259</t>
+          <t>358217; 431445</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>335345; 486187</t>
+          <t>341352; 487179</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>706186; 803807</t>
+          <t>711226; 805335</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>867953; 976539</t>
+          <t>871659; 977191</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>544270; 637888</t>
+          <t>545872; 637115</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>680531; 1391476</t>
+          <t>676326; 1420058</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1242138; 1385570</t>
+          <t>1249092; 1376110</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1392870; 1538054</t>
+          <t>1395615; 1537357</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>926931; 1047567</t>
+          <t>929739; 1047161</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1081742; 1871800</t>
+          <t>1084551; 1891444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,73</t>
+          <t>7,99; 13,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 12,97</t>
+          <t>7,38; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,2</t>
+          <t>4,73; 10,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,07</t>
+          <t>2,43; 10,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 19,9</t>
+          <t>13,48; 20,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 21,63</t>
+          <t>14,5; 21,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,45</t>
+          <t>7,74; 13,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 19,36</t>
+          <t>8,7; 19,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 15,85</t>
+          <t>11,46; 15,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,31</t>
+          <t>11,36; 16,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,58</t>
+          <t>6,94; 10,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,96</t>
+          <t>6,01; 12,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,01</t>
+          <t>12,17; 17,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,63</t>
+          <t>11,24; 16,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,11</t>
+          <t>7,07; 12,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,9</t>
+          <t>6,55; 14,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 22,46</t>
+          <t>16,17; 22,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,19; 23,99</t>
+          <t>16,77; 23,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,88</t>
+          <t>9,71; 14,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 14,02</t>
+          <t>9,21; 15,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,74</t>
+          <t>14,7; 18,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 18,81</t>
+          <t>14,78; 18,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 12,46</t>
+          <t>8,72; 12,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,3</t>
+          <t>8,61; 13,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,15</t>
+          <t>15,13; 21,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,14</t>
+          <t>13,98; 19,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,92</t>
+          <t>7,26; 12,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,63</t>
+          <t>8,2; 13,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,05; 25,63</t>
+          <t>18,73; 25,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 28,01</t>
+          <t>21,69; 28,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,08</t>
+          <t>9,84; 14,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 19,19</t>
+          <t>14,17; 19,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,26</t>
+          <t>17,94; 22,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 23,1</t>
+          <t>18,81; 23,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,6</t>
+          <t>9,12; 12,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 15,82</t>
+          <t>11,76; 15,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,96; 21,85</t>
+          <t>14,82; 21,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 18,77</t>
+          <t>12,55; 18,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 17,14</t>
+          <t>11,68; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,75</t>
+          <t>12,07; 17,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 27,26</t>
+          <t>19,14; 27,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,08; 32,47</t>
+          <t>24,73; 32,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,68</t>
+          <t>12,87; 18,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 21,15</t>
+          <t>17,42; 22,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,94</t>
+          <t>18,18; 23,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 24,75</t>
+          <t>19,42; 24,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,1; 17,12</t>
+          <t>13,18; 17,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 17,53</t>
+          <t>15,51; 19,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 25,75</t>
+          <t>17,14; 25,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,48; 24,22</t>
+          <t>16,04; 24,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,97</t>
+          <t>9,53; 15,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,05</t>
+          <t>14,99; 20,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,65; 31,42</t>
+          <t>22,54; 31,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 33,14</t>
+          <t>23,92; 33,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,49; 25,33</t>
+          <t>18,04; 25,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,56; 25,82</t>
+          <t>20,78; 26,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,13; 27,24</t>
+          <t>21,14; 27,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,33; 27,29</t>
+          <t>21,51; 27,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,48</t>
+          <t>14,56; 19,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 22,57</t>
+          <t>18,5; 22,43</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,61; 22,4</t>
+          <t>13,61; 22,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,64; 20,18</t>
+          <t>11,92; 20,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,25</t>
+          <t>10,53; 18,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 18,46</t>
+          <t>12,36; 18,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 32,72</t>
+          <t>23,42; 32,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,58</t>
+          <t>23,79; 33,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,33; 25,78</t>
+          <t>17,2; 25,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,86; 79,4</t>
+          <t>18,38; 23,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,93; 26,78</t>
+          <t>20,21; 26,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,5; 26,11</t>
+          <t>19,53; 26,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,69</t>
+          <t>15,06; 21,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 66,83</t>
+          <t>16,25; 20,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,16; 31,45</t>
+          <t>19,84; 31,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 28,73</t>
+          <t>17,58; 28,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,85; 23,56</t>
+          <t>14,75; 23,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 25,2</t>
+          <t>17,33; 25,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,6; 31,03</t>
+          <t>20,67; 30,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,8; 40,88</t>
+          <t>30,94; 41,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,78; 33,25</t>
+          <t>22,56; 33,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,81; 32,67</t>
+          <t>26,68; 33,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,91; 29,21</t>
+          <t>21,97; 29,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,35; 35,13</t>
+          <t>27,33; 34,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,18; 27,83</t>
+          <t>20,79; 28,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,96; 28,74</t>
+          <t>24,03; 29,08</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,67; 18,25</t>
+          <t>15,64; 18,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,58; 17,42</t>
+          <t>14,47; 17,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,72</t>
+          <t>10,62; 12,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,08</t>
+          <t>12,18; 14,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,83</t>
+          <t>21,04; 23,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,55; 27,52</t>
+          <t>24,43; 27,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,43; 18,01</t>
+          <t>15,32; 18,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 38,79</t>
+          <t>18,39; 20,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,68</t>
+          <t>18,66; 20,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,01; 22,04</t>
+          <t>19,94; 21,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,11</t>
+          <t>13,36; 15,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,23; 26,56</t>
+          <t>15,67; 17,33</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40826</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>69332</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40958; 67823</t>
+          <t>39478; 67682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33221; 58904</t>
+          <t>33520; 59729</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20957; 42796</t>
+          <t>19847; 42320</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9221; 44282</t>
+          <t>9928; 42421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62416; 93047</t>
+          <t>63022; 94314</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61322; 92625</t>
+          <t>62114; 93378</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30777; 53224</t>
+          <t>30643; 53668</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25209; 60624</t>
+          <t>31526; 70668</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109818; 152429</t>
+          <t>110222; 150543</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101012; 143920</t>
+          <t>100272; 141877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55429; 86237</t>
+          <t>56573; 87077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46566; 92430</t>
+          <t>46321; 95166</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52746</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90514</t>
+          <t>107295</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88683; 125135</t>
+          <t>89529; 127836</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76558; 114283</t>
+          <t>77251; 114018</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42293; 71493</t>
+          <t>41739; 71202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24714; 54658</t>
+          <t>31232; 67251</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>102547; 140507</t>
+          <t>101153; 141461</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104704; 146129</t>
+          <t>102132; 141694</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53619; 83883</t>
+          <t>54730; 83574</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34312; 71698</t>
+          <t>46149; 78258</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>199081; 255029</t>
+          <t>200130; 257759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>190260; 243823</t>
+          <t>191559; 245805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102793; 143809</t>
+          <t>100652; 142769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67613; 115046</t>
+          <t>84184; 131492</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89515</t>
+          <t>103597</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>151262</t>
+          <t>168381</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97395; 135084</t>
+          <t>96616; 134873</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95319; 137305</t>
+          <t>95306; 133775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47700; 79764</t>
+          <t>48588; 80718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48355; 78470</t>
+          <t>50915; 82184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>131386; 176769</t>
+          <t>129207; 174176</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152460; 198541</t>
+          <t>153776; 199444</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66225; 99331</t>
+          <t>64835; 98607</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75279; 104117</t>
+          <t>88178; 119425</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238652; 295707</t>
+          <t>238252; 296353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>258827; 321221</t>
+          <t>261572; 322317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121463; 167348</t>
+          <t>121071; 167610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131475; 170702</t>
+          <t>146229; 191660</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94300</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>132948</t>
+          <t>144905</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>227248</t>
+          <t>248396</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77675; 113431</t>
+          <t>76957; 112626</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76865; 115138</t>
+          <t>76987; 116300</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76111; 110559</t>
+          <t>75320; 110733</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36322; 139869</t>
+          <t>84599; 124613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101349; 140559</t>
+          <t>98711; 139368</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>154029; 199415</t>
+          <t>151879; 198378</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83878; 121265</t>
+          <t>83519; 121453</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>109624; 150805</t>
+          <t>128348; 162630</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185210; 237358</t>
+          <t>188133; 241715</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>243054; 303857</t>
+          <t>238385; 300478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>169513; 221487</t>
+          <t>170533; 221910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>140026; 280522</t>
+          <t>222907; 273679</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101174</t>
+          <t>108765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>127232</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>228406</t>
+          <t>250016</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66670; 99589</t>
+          <t>66269; 98317</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70770; 104016</t>
+          <t>68888; 103764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46102; 76176</t>
+          <t>45464; 76139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85112; 118127</t>
+          <t>91367; 127921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91506; 126945</t>
+          <t>91054; 126123</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108430; 148384</t>
+          <t>107129; 149248</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86502; 125268</t>
+          <t>89246; 125062</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>112640; 141468</t>
+          <t>126540; 158381</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>167060; 215358</t>
+          <t>167132; 213934</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187101; 239402</t>
+          <t>188695; 240856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>141381; 189268</t>
+          <t>141493; 192965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207179; 250307</t>
+          <t>225308; 273195</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56885</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>288844</t>
+          <t>91540</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>345729</t>
+          <t>153221</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39812; 65537</t>
+          <t>39822; 66573</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35944; 62311</t>
+          <t>36798; 63654</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35835; 61030</t>
+          <t>35202; 60661</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47439; 67803</t>
+          <t>50216; 74649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80798; 112192</t>
+          <t>80322; 112371</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>83780; 118538</t>
+          <t>83958; 117299</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65484; 97384</t>
+          <t>64963; 96664</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>120722; 482608</t>
+          <t>80610; 105183</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126635; 170184</t>
+          <t>128458; 169324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>129028; 172771</t>
+          <t>129253; 174159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108743; 147302</t>
+          <t>107246; 150561</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>171147; 651727</t>
+          <t>137292; 171294</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59578</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>126392</t>
+          <t>138276</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>185970</t>
+          <t>203045</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42306; 66002</t>
+          <t>41633; 66175</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42834; 71493</t>
+          <t>43752; 71516</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38173; 60553</t>
+          <t>37903; 59745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49830; 71258</t>
+          <t>53743; 77616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68775; 103612</t>
+          <t>69006; 103315</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>119821; 159019</t>
+          <t>120349; 160566</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90880; 132620</t>
+          <t>89987; 132249</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>114062; 138983</t>
+          <t>123837; 153790</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119146; 158838</t>
+          <t>119485; 160392</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174486; 224054</t>
+          <t>174320; 223009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138943; 182558</t>
+          <t>136345; 186528</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>169710; 203518</t>
+          <t>186052; 225154</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>434995</t>
+          <t>472094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>858503</t>
+          <t>727593</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1293498</t>
+          <t>1199687</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>513326; 598104</t>
+          <t>512557; 598780</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>499111; 596268</t>
+          <t>495542; 587182</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>358217; 431445</t>
+          <t>360374; 434948</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>341352; 487179</t>
+          <t>430206; 515362</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>711226; 805335</t>
+          <t>710915; 807951</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>871659; 977191</t>
+          <t>867361; 978350</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>545872; 637115</t>
+          <t>542145; 637600</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>676326; 1420058</t>
+          <t>686740; 769919</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1249092; 1376110</t>
+          <t>1241836; 1377343</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1395615; 1537357</t>
+          <t>1390928; 1532087</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>929739; 1047161</t>
+          <t>926230; 1045018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1084551; 1891444</t>
+          <t>1138565; 1259407</t>
         </is>
       </c>
     </row>
